--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.47742269363302</v>
+        <v>3.490081187715366</v>
       </c>
       <c r="D2" t="n">
-        <v>45.18677390007023</v>
+        <v>7.342850758761412</v>
       </c>
       <c r="E2" t="n">
-        <v>6.899102495579943</v>
+        <v>1.121104155531741</v>
       </c>
       <c r="F2" t="n">
-        <v>9.691912649506381</v>
+        <v>1.574935805544787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.10090294601639</v>
+        <v>5.216396728727664</v>
       </c>
       <c r="D3" t="n">
-        <v>31.5872128363483</v>
+        <v>5.1329220859066</v>
       </c>
       <c r="E3" t="n">
-        <v>6.899102495579943</v>
+        <v>1.121104155531741</v>
       </c>
       <c r="F3" t="n">
-        <v>9.691912649506381</v>
+        <v>1.574935805544787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.18660311114763</v>
+        <v>6.042823005561489</v>
       </c>
       <c r="D4" t="n">
-        <v>45.03028690974639</v>
+        <v>7.317421622833788</v>
       </c>
       <c r="E4" t="n">
-        <v>6.899102495579943</v>
+        <v>1.121104155531741</v>
       </c>
       <c r="F4" t="n">
-        <v>9.691912649506381</v>
+        <v>1.574935805544787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.17091561389608</v>
+        <v>3.440273787258113</v>
       </c>
       <c r="D5" t="n">
-        <v>22.2044530609887</v>
+        <v>3.608223622410664</v>
       </c>
       <c r="E5" t="n">
-        <v>6.899102495579943</v>
+        <v>1.121104155531741</v>
       </c>
       <c r="F5" t="n">
-        <v>9.691912649506381</v>
+        <v>1.574935805544787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
